--- a/table/Datas/#Action.xlsx
+++ b/table/Datas/#Action.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>class</t>
+          <t>category</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>class</t>
+          <t>category</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
